--- a/excel_db/settings.xlsx
+++ b/excel_db/settings.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>key</t>
   </si>
@@ -23,6 +23,21 @@
   </si>
   <si>
     <t>updated_at</t>
+  </si>
+  <si>
+    <t>result_is_active</t>
+  </si>
+  <si>
+    <t>result_deadline</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2026-12-12</t>
+  </si>
+  <si>
+    <t>2026-06-06 13:05</t>
   </si>
 </sst>
 </file>
@@ -380,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -394,6 +409,28 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
